--- a/contents/tables/reproduced/table1_reproduced.xlsx
+++ b/contents/tables/reproduced/table1_reproduced.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dalu-my.sharepoint.com/personal/ku753523_dal_ca/Documents/COURSES/CSCI 6055 - Research Methods &amp; Statistics/Research-Methodology-and-Stats/PROJECT/contents/tables/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dalu-my.sharepoint.com/personal/ku753523_dal_ca/Documents/COURSES/CSCI 6055 - Research Methods &amp; Statistics/Research-Methodology-and-Stats/contents/tables/reproduced/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="11_F25DC773A252ABDACC1048EB319F45B05ADE58F6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B40A8573-77B5-4BDB-AC00-45F8DDC61ABB}"/>
+  <xr:revisionPtr revIDLastSave="95" documentId="11_F25DC773A252ABDACC1048EB319F45B05ADE58F6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F78FA76-9753-4330-86DE-F4277283EED7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="77">
   <si>
     <t>Feature Name</t>
   </si>
@@ -242,13 +242,31 @@
     <t>Thalassemia</t>
   </si>
   <si>
-    <t>Normal</t>
-  </si>
-  <si>
-    <t>Fixed defect</t>
-  </si>
-  <si>
-    <t>Reversible</t>
+    <t>Data Type</t>
+  </si>
+  <si>
+    <t>Ratio</t>
+  </si>
+  <si>
+    <t>Nominal</t>
+  </si>
+  <si>
+    <t>Interval</t>
+  </si>
+  <si>
+    <t>3 = Reversible</t>
+  </si>
+  <si>
+    <t>2 = Fixed defect</t>
+  </si>
+  <si>
+    <t>1 = Normal</t>
+  </si>
+  <si>
+    <t>0 = Null</t>
+  </si>
+  <si>
+    <t>Ordinal</t>
   </si>
 </sst>
 </file>
@@ -371,7 +389,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -382,29 +400,44 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -686,1019 +719,1138 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="55.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.6640625" customWidth="1"/>
+    <col min="3" max="3" width="21.21875" style="16" customWidth="1"/>
+    <col min="4" max="4" width="33.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="6">
+      <c r="E2" s="4">
         <v>23</v>
       </c>
-      <c r="E2" s="6">
+      <c r="F2" s="4">
         <v>45</v>
       </c>
-      <c r="F2" s="6">
+      <c r="G2" s="4">
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="7"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="6" t="s">
+      <c r="B3" s="10"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="6">
+      <c r="E3" s="4">
         <v>155</v>
       </c>
-      <c r="E3" s="6">
+      <c r="F3" s="4">
         <v>283</v>
       </c>
-      <c r="F3" s="6">
+      <c r="G3" s="4">
         <v>438</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="7"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="6" t="s">
+      <c r="B4" s="10"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="6">
+      <c r="E4" s="4">
         <v>318</v>
       </c>
-      <c r="E4" s="6">
+      <c r="F4" s="4">
         <v>181</v>
       </c>
-      <c r="F4" s="6">
+      <c r="G4" s="4">
         <v>499</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="7"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="6" t="s">
+      <c r="B5" s="10"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="6">
+      <c r="E5" s="4">
         <v>3</v>
       </c>
-      <c r="E5" s="6">
+      <c r="F5" s="4">
         <v>17</v>
       </c>
-      <c r="F5" s="6">
+      <c r="G5" s="4">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="9"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="11" t="s">
+    <row r="6" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="8"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="11">
+      <c r="E6" s="5">
         <v>499</v>
       </c>
-      <c r="E6" s="11">
+      <c r="F6" s="5">
         <v>526</v>
       </c>
-      <c r="F6" s="11">
+      <c r="G6" s="5">
         <v>1025</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="6">
+      <c r="E7" s="4">
         <v>413</v>
       </c>
-      <c r="E7" s="6">
+      <c r="F7" s="4">
         <v>300</v>
       </c>
-      <c r="F7" s="6">
+      <c r="G7" s="4">
         <v>713</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="7"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="6" t="s">
+      <c r="B8" s="10"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="6">
+      <c r="E8" s="4">
         <v>86</v>
       </c>
-      <c r="E8" s="6">
+      <c r="F8" s="4">
         <v>226</v>
       </c>
-      <c r="F8" s="6">
+      <c r="G8" s="4">
         <v>312</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="9"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="11" t="s">
+    <row r="9" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="8"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="11">
+      <c r="E9" s="5">
         <v>499</v>
       </c>
-      <c r="E9" s="11">
+      <c r="F9" s="5">
         <v>526</v>
       </c>
-      <c r="F9" s="11">
+      <c r="G9" s="5">
         <v>1025</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
+    <row r="10" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="6">
+      <c r="E10" s="4">
         <v>375</v>
       </c>
-      <c r="E10" s="6">
+      <c r="F10" s="4">
         <v>122</v>
       </c>
-      <c r="F10" s="6">
+      <c r="G10" s="4">
         <v>497</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="7"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="6" t="s">
+      <c r="B11" s="10"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="6">
+      <c r="E11" s="4">
         <v>33</v>
       </c>
-      <c r="E11" s="6">
+      <c r="F11" s="4">
         <v>134</v>
       </c>
-      <c r="F11" s="6">
+      <c r="G11" s="4">
         <v>167</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="7"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="6" t="s">
+      <c r="B12" s="10"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="6">
+      <c r="E12" s="4">
         <v>65</v>
       </c>
-      <c r="E12" s="6">
+      <c r="F12" s="4">
         <v>219</v>
       </c>
-      <c r="F12" s="6">
+      <c r="G12" s="4">
         <v>284</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="7"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="6" t="s">
+      <c r="B13" s="10"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="6">
+      <c r="E13" s="4">
         <v>26</v>
       </c>
-      <c r="E13" s="6">
+      <c r="F13" s="4">
         <v>51</v>
       </c>
-      <c r="F13" s="6">
+      <c r="G13" s="4">
         <v>77</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="9"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="11" t="s">
+    <row r="14" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="8"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D14" s="11">
+      <c r="E14" s="5">
         <v>499</v>
       </c>
-      <c r="E14" s="11">
+      <c r="F14" s="5">
         <v>526</v>
       </c>
-      <c r="F14" s="11">
+      <c r="G14" s="5">
         <v>1025</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="4" t="s">
+    <row r="15" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="6">
+      <c r="E15" s="4">
         <v>138</v>
       </c>
-      <c r="E15" s="6">
+      <c r="F15" s="4">
         <v>191</v>
       </c>
-      <c r="F15" s="6">
+      <c r="G15" s="4">
         <v>329</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="7"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="6" t="s">
+      <c r="B16" s="10"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="6">
+      <c r="E16" s="4">
         <v>287</v>
       </c>
-      <c r="E16" s="6">
+      <c r="F16" s="4">
         <v>294</v>
       </c>
-      <c r="F16" s="6">
+      <c r="G16" s="4">
         <v>581</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="7"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="6" t="s">
+      <c r="B17" s="10"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="6">
+      <c r="E17" s="4">
         <v>67</v>
       </c>
-      <c r="E17" s="6">
+      <c r="F17" s="4">
         <v>41</v>
       </c>
-      <c r="F17" s="6">
+      <c r="G17" s="4">
         <v>108</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="7"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="6" t="s">
+      <c r="B18" s="10"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="6">
+      <c r="E18" s="4">
         <v>7</v>
       </c>
-      <c r="E18" s="6">
+      <c r="F18" s="4">
         <v>0</v>
       </c>
-      <c r="F18" s="6">
+      <c r="G18" s="4">
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="9"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="11" t="s">
+    <row r="19" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="8"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D19" s="11">
+      <c r="E19" s="5">
         <v>499</v>
       </c>
-      <c r="E19" s="11">
+      <c r="F19" s="5">
         <v>526</v>
       </c>
-      <c r="F19" s="11">
+      <c r="G19" s="5">
         <v>1025</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="4" t="s">
+    <row r="20" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="6">
+      <c r="E20" s="4">
         <v>189</v>
       </c>
-      <c r="E20" s="6">
+      <c r="F20" s="4">
         <v>247</v>
       </c>
-      <c r="F20" s="6">
+      <c r="G20" s="4">
         <v>436</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="7"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="6" t="s">
+      <c r="B21" s="10"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="6">
+      <c r="E21" s="4">
         <v>299</v>
       </c>
-      <c r="E21" s="6">
+      <c r="F21" s="4">
         <v>264</v>
       </c>
-      <c r="F21" s="6">
+      <c r="G21" s="4">
         <v>563</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="7"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="6" t="s">
+      <c r="B22" s="10"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="6">
+      <c r="E22" s="4">
         <v>11</v>
       </c>
-      <c r="E22" s="6">
+      <c r="F22" s="4">
         <v>12</v>
       </c>
-      <c r="F22" s="6">
+      <c r="G22" s="4">
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="7"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="6" t="s">
+      <c r="B23" s="10"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D23" s="6">
+      <c r="E23" s="4">
         <v>0</v>
       </c>
-      <c r="E23" s="6">
+      <c r="F23" s="4">
         <v>3</v>
       </c>
-      <c r="F23" s="6">
+      <c r="G23" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="9"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="11" t="s">
+    <row r="24" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="8"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D24" s="11">
+      <c r="E24" s="5">
         <v>499</v>
       </c>
-      <c r="E24" s="11">
+      <c r="F24" s="5">
         <v>526</v>
       </c>
-      <c r="F24" s="11">
+      <c r="G24" s="5">
         <v>1025</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="4" t="s">
+    <row r="25" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="6">
+      <c r="E25" s="4">
         <v>417</v>
       </c>
-      <c r="E25" s="6">
+      <c r="F25" s="4">
         <v>455</v>
       </c>
-      <c r="F25" s="6">
+      <c r="G25" s="4">
         <v>872</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="7"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="6" t="s">
+      <c r="B26" s="10"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="6">
+      <c r="E26" s="4">
         <v>82</v>
       </c>
-      <c r="E26" s="6">
+      <c r="F26" s="4">
         <v>71</v>
       </c>
-      <c r="F26" s="6">
+      <c r="G26" s="4">
         <v>153</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="9"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="11" t="s">
+    <row r="27" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="8"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D27" s="11">
+      <c r="E27" s="5">
         <v>499</v>
       </c>
-      <c r="E27" s="11">
+      <c r="F27" s="5">
         <v>526</v>
       </c>
-      <c r="F27" s="11">
+      <c r="G27" s="5">
         <v>1025</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="4" t="s">
+    <row r="28" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="D28" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D28" s="6">
+      <c r="E28" s="4">
         <v>283</v>
       </c>
-      <c r="E28" s="6">
+      <c r="F28" s="4">
         <v>214</v>
       </c>
-      <c r="F28" s="6">
+      <c r="G28" s="4">
         <v>497</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="7"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="6" t="s">
+      <c r="B29" s="10"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D29" s="6">
+      <c r="E29" s="4">
         <v>204</v>
       </c>
-      <c r="E29" s="6">
+      <c r="F29" s="4">
         <v>309</v>
       </c>
-      <c r="F29" s="6">
+      <c r="G29" s="4">
         <v>513</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="7"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="6" t="s">
+      <c r="B30" s="10"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D30" s="6">
+      <c r="E30" s="4">
         <v>12</v>
       </c>
-      <c r="E30" s="6">
+      <c r="F30" s="4">
         <v>3</v>
       </c>
-      <c r="F30" s="6">
+      <c r="G30" s="4">
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="9"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="11" t="s">
+    <row r="31" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="8"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D31" s="11">
+      <c r="E31" s="5">
         <v>499</v>
       </c>
-      <c r="E31" s="11">
+      <c r="F31" s="5">
         <v>526</v>
       </c>
-      <c r="F31" s="11">
+      <c r="G31" s="5">
         <v>1025</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="4" t="s">
+    <row r="32" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D32" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D32" s="6">
+      <c r="E32" s="4">
         <v>40</v>
       </c>
-      <c r="E32" s="6">
+      <c r="F32" s="4">
         <v>6</v>
       </c>
-      <c r="F32" s="6">
+      <c r="G32" s="4">
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="7"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="6" t="s">
+      <c r="B33" s="10"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D33" s="6">
+      <c r="E33" s="4">
         <v>197</v>
       </c>
-      <c r="E33" s="6">
+      <c r="F33" s="4">
         <v>77</v>
       </c>
-      <c r="F33" s="6">
+      <c r="G33" s="4">
         <v>274</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="7"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="6" t="s">
+      <c r="B34" s="10"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D34" s="6">
+      <c r="E34" s="4">
         <v>248</v>
       </c>
-      <c r="E34" s="6">
+      <c r="F34" s="4">
         <v>357</v>
       </c>
-      <c r="F34" s="6">
+      <c r="G34" s="4">
         <v>605</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="7"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="6" t="s">
+      <c r="B35" s="10"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D35" s="6">
+      <c r="E35" s="4">
         <v>14</v>
       </c>
-      <c r="E35" s="6">
+      <c r="F35" s="4">
         <v>86</v>
       </c>
-      <c r="F35" s="6">
+      <c r="G35" s="4">
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="9"/>
-      <c r="B36" s="10"/>
-      <c r="C36" s="11" t="s">
+    <row r="36" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="8"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D36" s="11">
+      <c r="E36" s="5">
         <v>499</v>
       </c>
-      <c r="E36" s="11">
+      <c r="F36" s="5">
         <v>526</v>
       </c>
-      <c r="F36" s="11">
+      <c r="G36" s="5">
         <v>1025</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="4" t="s">
+    <row r="37" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D37" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D37" s="6">
+      <c r="E37" s="4">
         <v>225</v>
       </c>
-      <c r="E37" s="6">
+      <c r="F37" s="4">
         <v>455</v>
       </c>
-      <c r="F37" s="6">
+      <c r="G37" s="4">
         <v>680</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="7"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="6" t="s">
+      <c r="B38" s="10"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="6">
+      <c r="E38" s="4">
         <v>274</v>
       </c>
-      <c r="E38" s="6">
+      <c r="F38" s="4">
         <v>71</v>
       </c>
-      <c r="F38" s="6">
+      <c r="G38" s="4">
         <v>345</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="9"/>
-      <c r="B39" s="10"/>
-      <c r="C39" s="11" t="s">
+    <row r="39" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="8"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D39" s="11">
+      <c r="E39" s="5">
         <v>499</v>
       </c>
-      <c r="E39" s="11">
+      <c r="F39" s="5">
         <v>526</v>
       </c>
-      <c r="F39" s="11">
+      <c r="G39" s="5">
         <v>1025</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="4" t="s">
+    <row r="40" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="D40" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D40" s="6">
+      <c r="E40" s="4">
         <v>265</v>
       </c>
-      <c r="E40" s="6">
+      <c r="F40" s="4">
         <v>461</v>
       </c>
-      <c r="F40" s="6">
+      <c r="G40" s="4">
         <v>726</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="7"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="6" t="s">
+      <c r="B41" s="10"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D41" s="6">
+      <c r="E41" s="4">
         <v>167</v>
       </c>
-      <c r="E41" s="6">
+      <c r="F41" s="4">
         <v>59</v>
       </c>
-      <c r="F41" s="6">
+      <c r="G41" s="4">
         <v>226</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="7"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="6" t="s">
+      <c r="B42" s="10"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D42" s="6">
+      <c r="E42" s="4">
         <v>60</v>
       </c>
-      <c r="E42" s="6">
+      <c r="F42" s="4">
         <v>6</v>
       </c>
-      <c r="F42" s="6">
+      <c r="G42" s="4">
         <v>66</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="7"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="6" t="s">
+      <c r="B43" s="10"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D43" s="6">
+      <c r="E43" s="4">
         <v>7</v>
       </c>
-      <c r="E43" s="6">
+      <c r="F43" s="4">
         <v>0</v>
       </c>
-      <c r="F43" s="6">
+      <c r="G43" s="4">
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="9"/>
-      <c r="B44" s="10"/>
-      <c r="C44" s="11" t="s">
+    <row r="44" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="8"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D44" s="11">
+      <c r="E44" s="5">
         <v>499</v>
       </c>
-      <c r="E44" s="11">
+      <c r="F44" s="5">
         <v>526</v>
       </c>
-      <c r="F44" s="11">
+      <c r="G44" s="5">
         <v>1025</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="4" t="s">
+    <row r="45" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B45" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C45" s="6" t="s">
+      <c r="C45" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="D45" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D45" s="6">
+      <c r="E45" s="4">
         <v>46</v>
       </c>
-      <c r="E45" s="6">
+      <c r="F45" s="4">
         <v>28</v>
       </c>
-      <c r="F45" s="6">
+      <c r="G45" s="4">
         <v>74</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="7"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="6" t="s">
+      <c r="B46" s="10"/>
+      <c r="C46" s="13"/>
+      <c r="D46" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D46" s="6">
+      <c r="E46" s="4">
         <v>324</v>
       </c>
-      <c r="E46" s="6">
+      <c r="F46" s="4">
         <v>158</v>
       </c>
-      <c r="F46" s="6">
+      <c r="G46" s="4">
         <v>482</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="7"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="6" t="s">
+      <c r="B47" s="10"/>
+      <c r="C47" s="13"/>
+      <c r="D47" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D47" s="6">
+      <c r="E47" s="4">
         <v>129</v>
       </c>
-      <c r="E47" s="6">
+      <c r="F47" s="4">
         <v>340</v>
       </c>
-      <c r="F47" s="6">
+      <c r="G47" s="4">
         <v>469</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="9"/>
-      <c r="B48" s="10"/>
-      <c r="C48" s="11" t="s">
+    <row r="48" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="8"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="14"/>
+      <c r="D48" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D48" s="11">
+      <c r="E48" s="5">
         <v>499</v>
       </c>
-      <c r="E48" s="11">
+      <c r="F48" s="5">
         <v>526</v>
       </c>
-      <c r="F48" s="11">
+      <c r="G48" s="5">
         <v>1025</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="4" t="s">
+    <row r="49" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="B49" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C49" s="6">
+      <c r="C49" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="D49" s="4">
         <v>0</v>
       </c>
-      <c r="D49" s="6">
+      <c r="E49" s="4">
         <v>163</v>
       </c>
-      <c r="E49" s="6">
+      <c r="F49" s="4">
         <v>415</v>
       </c>
-      <c r="F49" s="6">
+      <c r="G49" s="4">
         <v>578</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="7"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="6">
+      <c r="B50" s="10"/>
+      <c r="C50" s="13"/>
+      <c r="D50" s="4">
         <v>1</v>
       </c>
-      <c r="D50" s="6">
+      <c r="E50" s="4">
         <v>160</v>
       </c>
-      <c r="E50" s="6">
+      <c r="F50" s="4">
         <v>66</v>
       </c>
-      <c r="F50" s="6">
+      <c r="G50" s="4">
         <v>226</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="7"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="6">
+      <c r="B51" s="10"/>
+      <c r="C51" s="13"/>
+      <c r="D51" s="4">
         <v>2</v>
       </c>
-      <c r="D51" s="6">
+      <c r="E51" s="4">
         <v>113</v>
       </c>
-      <c r="E51" s="6">
+      <c r="F51" s="4">
         <v>21</v>
       </c>
-      <c r="F51" s="6">
+      <c r="G51" s="4">
         <v>134</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="7"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="6">
+      <c r="B52" s="10"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="4">
         <v>3</v>
       </c>
-      <c r="D52" s="6">
+      <c r="E52" s="4">
         <v>60</v>
       </c>
-      <c r="E52" s="6">
+      <c r="F52" s="4">
         <v>9</v>
       </c>
-      <c r="F52" s="6">
+      <c r="G52" s="4">
         <v>69</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="7"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="6">
+      <c r="B53" s="10"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="4">
         <v>4</v>
       </c>
-      <c r="D53" s="6">
+      <c r="E53" s="4">
         <v>3</v>
       </c>
-      <c r="E53" s="6">
+      <c r="F53" s="4">
         <v>15</v>
       </c>
-      <c r="F53" s="6">
+      <c r="G53" s="4">
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="9"/>
-      <c r="B54" s="10"/>
-      <c r="C54" s="11" t="s">
+    <row r="54" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="8"/>
+      <c r="B54" s="11"/>
+      <c r="C54" s="14"/>
+      <c r="D54" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D54" s="11">
+      <c r="E54" s="5">
         <v>499</v>
       </c>
-      <c r="E54" s="11">
+      <c r="F54" s="5">
         <v>526</v>
       </c>
-      <c r="F54" s="11">
+      <c r="G54" s="5">
         <v>1025</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="4" t="s">
+    <row r="55" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B55" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C55" s="6">
-        <v>0</v>
-      </c>
-      <c r="D55" s="6">
+      <c r="C55" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E55" s="4">
         <v>4</v>
       </c>
-      <c r="E55" s="6">
+      <c r="F55" s="4">
         <v>3</v>
       </c>
-      <c r="F55" s="6">
+      <c r="G55" s="4">
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="7"/>
-      <c r="B56" s="8"/>
-      <c r="C56" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D56" s="6">
+      <c r="B56" s="10"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E56" s="4">
         <v>43</v>
       </c>
-      <c r="E56" s="6">
+      <c r="F56" s="4">
         <v>21</v>
       </c>
-      <c r="F56" s="6">
+      <c r="G56" s="4">
         <v>64</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="7"/>
-      <c r="B57" s="8"/>
-      <c r="C57" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D57" s="6">
+      <c r="B57" s="10"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E57" s="4">
         <v>132</v>
       </c>
-      <c r="E57" s="6">
+      <c r="F57" s="4">
         <v>412</v>
       </c>
-      <c r="F57" s="6">
+      <c r="G57" s="4">
         <v>544</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="7"/>
-      <c r="B58" s="8"/>
-      <c r="C58" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D58" s="6">
+      <c r="B58" s="10"/>
+      <c r="C58" s="13"/>
+      <c r="D58" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E58" s="4">
         <v>320</v>
       </c>
-      <c r="E58" s="6">
+      <c r="F58" s="4">
         <v>90</v>
       </c>
-      <c r="F58" s="6">
+      <c r="G58" s="4">
         <v>410</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="9"/>
-      <c r="B59" s="10"/>
-      <c r="C59" s="11" t="s">
+    <row r="59" spans="1:7" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="8"/>
+      <c r="B59" s="11"/>
+      <c r="C59" s="14"/>
+      <c r="D59" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D59" s="11">
+      <c r="E59" s="5">
         <v>499</v>
       </c>
-      <c r="E59" s="11">
+      <c r="F59" s="5">
         <v>526</v>
       </c>
-      <c r="F59" s="11">
+      <c r="G59" s="5">
         <v>1025</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="39">
+    <mergeCell ref="C45:C48"/>
+    <mergeCell ref="C49:C54"/>
+    <mergeCell ref="C55:C59"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="C28:C31"/>
+    <mergeCell ref="C32:C36"/>
+    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="C40:C44"/>
+    <mergeCell ref="C2:C6"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="C10:C14"/>
+    <mergeCell ref="C15:C19"/>
+    <mergeCell ref="C20:C24"/>
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="A10:A14"/>
+    <mergeCell ref="B10:B14"/>
+    <mergeCell ref="A15:A19"/>
+    <mergeCell ref="B15:B19"/>
+    <mergeCell ref="A20:A24"/>
+    <mergeCell ref="B20:B24"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="A28:A31"/>
+    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="A32:A36"/>
+    <mergeCell ref="B32:B36"/>
+    <mergeCell ref="A37:A39"/>
+    <mergeCell ref="B37:B39"/>
     <mergeCell ref="A55:A59"/>
     <mergeCell ref="B55:B59"/>
     <mergeCell ref="A40:A44"/>
@@ -1707,24 +1859,6 @@
     <mergeCell ref="B45:B48"/>
     <mergeCell ref="A49:A54"/>
     <mergeCell ref="B49:B54"/>
-    <mergeCell ref="A28:A31"/>
-    <mergeCell ref="B28:B31"/>
-    <mergeCell ref="A32:A36"/>
-    <mergeCell ref="B32:B36"/>
-    <mergeCell ref="A37:A39"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="A15:A19"/>
-    <mergeCell ref="B15:B19"/>
-    <mergeCell ref="A20:A24"/>
-    <mergeCell ref="B20:B24"/>
-    <mergeCell ref="A25:A27"/>
-    <mergeCell ref="B25:B27"/>
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="B2:B6"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="A10:A14"/>
-    <mergeCell ref="B10:B14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
